--- a/manga-import.xlsx
+++ b/manga-import.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\!ДИПЛООООООМ\manga-server\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\!Диплом 2.0\Forgotten-team-master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B839C102-0AA7-4BF5-8C8B-6C09B84B21FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E259A55D-299B-4C72-8743-B425F2F6CDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13560" yWindow="1305" windowWidth="15975" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12825" yWindow="1305" windowWidth="15975" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="69">
   <si>
     <t>id</t>
   </si>
@@ -217,6 +217,21 @@
   </si>
   <si>
     <t>2026-03-13T04:34:32.982Z</t>
+  </si>
+  <si>
+    <t>орррр</t>
+  </si>
+  <si>
+    <t>рпрпрр</t>
+  </si>
+  <si>
+    <t>орерорпрор</t>
+  </si>
+  <si>
+    <t>рр</t>
+  </si>
+  <si>
+    <t>"Гарем"</t>
   </si>
 </sst>
 </file>
@@ -540,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" customWidth="1"/>
@@ -890,6 +905,44 @@
         <v>63</v>
       </c>
     </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2026</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
